--- a/output/laminas_comunales/comunal_o_ocup_a_2019_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2019_la_araucania.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>39.8517875671387</v>
+        <v>60.6133728027344</v>
       </c>
     </row>
     <row r="3">
@@ -399,37 +399,37 @@
         </is>
       </c>
       <c r="C3">
-        <v>37.915470123291</v>
+        <v>58.7631874084473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.3946762084961</v>
+        <v>54.1758117675781</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C5">
-        <v>36.1258010864258</v>
+        <v>54.0469245910645</v>
       </c>
     </row>
     <row r="6">
@@ -444,412 +444,3292 @@
         </is>
       </c>
       <c r="C6">
-        <v>35.6708641052246</v>
+        <v>53.473445892334</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C7">
-        <v>35.3276710510254</v>
+        <v>53.3212280273438</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C8">
-        <v>34.5038452148438</v>
+        <v>52.1060218811035</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C9">
-        <v>34.0254249572754</v>
+        <v>52.0015411376953</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C10">
-        <v>33.6698036193848</v>
+        <v>51.638843536377</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C11">
-        <v>33.3869247436523</v>
+        <v>51.3617515563965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C12">
-        <v>32.2845840454102</v>
+        <v>51.2931022644043</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C13">
-        <v>31.6241760253906</v>
+        <v>50.986442565918</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C14">
-        <v>31.5444145202637</v>
+        <v>50.6760063171387</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C15">
-        <v>31.2768802642822</v>
+        <v>50.523021697998</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C16">
-        <v>31.2715663909912</v>
+        <v>50.0645980834961</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C17">
-        <v>30.9727210998535</v>
+        <v>49.4763298034668</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C18">
-        <v>29.9425964355469</v>
+        <v>48.6889533996582</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C19">
-        <v>29.4651393890381</v>
+        <v>48.619327545166</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C20">
-        <v>28.5959815979004</v>
+        <v>48.4285125732422</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C21">
-        <v>27.4750480651855</v>
+        <v>47.930477142334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C22">
-        <v>27.3444232940674</v>
+        <v>47.6063270568848</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C23">
-        <v>27.1405277252197</v>
+        <v>46.575798034668</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="C24">
-        <v>26.2082328796387</v>
+        <v>46.5011520385742</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C25">
-        <v>25.9487552642822</v>
+        <v>46.2756500244141</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C26">
-        <v>25.5977191925049</v>
+        <v>46.1352081298828</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C27">
-        <v>25.0757732391357</v>
+        <v>46.0277786254883</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C28">
-        <v>24.8583240509033</v>
+        <v>45.9956512451172</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C29">
-        <v>24.3277606964111</v>
+        <v>45.304817199707</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C30">
-        <v>24.2757816314697</v>
+        <v>45.2028770446777</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C31">
-        <v>23.5276832580566</v>
+        <v>44.8672790527344</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="C32">
-        <v>20.2792663574219</v>
+        <v>44.5993995666504</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>44.462158203125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>44.4368095397949</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>43.9688262939453</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>43.86279296875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>43.600154876709</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>43.0071029663086</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>42.875316619873</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>42.7168960571289</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>42.1808967590332</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>42.0698127746582</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>41.7359657287598</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>40.6701316833496</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>40.5685615539551</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>40.5262184143066</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>40.3842887878418</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>40.2143630981445</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>39.9978790283203</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>39.9688606262207</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>39.8517875671387</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>39.7638931274414</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>39.5841217041016</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>39.2068519592285</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>39.1893272399902</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>39.0154151916504</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>38.9692001342773</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>38.2768363952637</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>38.2340316772461</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>38.1132888793945</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>37.9514427185059</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>37.915470123291</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>37.6373023986816</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>37.2061653137207</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>37.0849914550781</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>36.8646507263184</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>36.4771003723145</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>36.452709197998</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>36.3946762084961</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>36.1258010864258</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>35.9839286804199</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>35.8982238769531</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>35.6708641052246</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>35.6704788208008</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>35.6070098876953</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>35.5054969787598</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>35.3276710510254</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>9116</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="C33">
+      <c r="C78">
+        <v>34.6850814819336</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>34.5038452148438</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>34.4291038513184</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>34.2790184020996</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>34.2377624511719</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>34.0254249572754</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>34.0204544067383</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>33.9439468383789</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>33.9173545837402</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>33.8854064941406</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>33.7198715209961</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>33.6698036193848</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>33.5138740539551</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>33.3869247436523</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>33.2698822021484</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>33.1951293945312</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>33.1718482971191</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>33.0611801147461</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>32.9638748168945</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>32.7990379333496</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>32.5425224304199</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>32.2845840454102</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>32.2432403564453</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>32.2155570983887</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>31.7980041503906</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>31.6241760253906</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>31.5444145202637</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>31.4356937408447</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>31.2768802642822</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>31.2715663909912</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>31.1870136260986</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>31.0460815429688</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>30.9727210998535</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>30.8912830352783</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>30.8717994689941</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>30.8444576263428</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>30.7862777709961</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>30.5031051635742</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>30.3667850494385</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>30.2862720489502</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>30.2627296447754</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>30.106294631958</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>30.0959815979004</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>29.9425964355469</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>29.4651393890381</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>29.2819995880127</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>29.2391662597656</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>29.1340179443359</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>29.0645122528076</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>29.0179710388184</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>28.7032642364502</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>28.6275291442871</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>28.5959815979004</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>28.5207176208496</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>28.3736515045166</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>28.3439769744873</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>28.2728824615479</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>28.235445022583</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>28.2067756652832</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>28.0103664398193</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>27.9226970672607</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>27.745189666748</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>27.6074867248535</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>27.5168533325195</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>27.4750480651855</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>27.3444232940674</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>27.2730026245117</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>27.1540660858154</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>27.1405277252197</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>26.9724292755127</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>26.7926025390625</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>26.6302165985107</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>26.2082328796387</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>26.1619644165039</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>26.0854396820068</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>26.0126037597656</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>25.9901905059814</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>25.9487552642822</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>25.9381103515625</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>25.659517288208</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>25.6189670562744</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>25.5977191925049</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>25.4198608398438</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>25.4030323028564</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>25.0757732391357</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>24.8583240509033</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>24.7331523895264</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>24.3277606964111</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>24.3153438568115</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>24.2757816314697</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>23.8764038085938</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>23.8603057861328</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>23.7265853881836</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>23.5276832580566</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>23.3338031768799</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>23.019172668457</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>22.6567535400391</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>22.6389331817627</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>22.0086116790771</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>21.5421447753906</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>21.5105381011963</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>21.2925205230713</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>21.2155246734619</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>20.8274707794189</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>20.4407615661621</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>20.2792663574219</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>20.2251167297363</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>20.037389755249</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>19.7961120605469</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C187">
         <v>19.4605197906494</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>19.0978870391846</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>19.0087985992432</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>18.9446716308594</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>18.9408264160156</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>18.80517578125</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>18.1497440338135</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>9.893667221069339</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>9.28468227386475</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>9.24529457092285</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>8.89495372772217</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>8.85157585144043</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>8.74344635009766</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>8.4228048324585</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>8.20086765289307</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>8.081917762756349</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>8.054801940917971</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>7.1366081237793</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>7.12859439849854</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>7.01394748687744</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>7.00369358062744</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>6.95270204544067</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>6.84690284729004</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>6.70897531509399</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>6.37082624435425</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>6.20015954971313</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>6.041419506073</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>5.91458559036255</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>5.7783203125</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>5.45862865447998</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>5.29488134384155</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>5.08429908752441</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>4.71067810058594</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>4.52338933944702</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>4.47464895248413</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>3.99872040748596</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>3.73614859580994</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>3.24257898330688</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>3.09102463722229</v>
       </c>
     </row>
   </sheetData>
